--- a/research/traditional_assets/database/data/united_kingdom/united_kingdom_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/united_kingdom/united_kingdom_insurance_prop_cas.xlsx
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.06985</v>
+        <v>0.07195</v>
       </c>
       <c r="E2">
-        <v>-0.03373</v>
+        <v>-0.04289999999999999</v>
       </c>
       <c r="F2">
-        <v>0.0667</v>
+        <v>0.14985</v>
       </c>
       <c r="G2">
-        <v>0.1791085589280831</v>
+        <v>0.2427902691138624</v>
       </c>
       <c r="H2">
-        <v>0.1791085589280831</v>
+        <v>0.2427902691138624</v>
       </c>
       <c r="I2">
-        <v>0.225979602791197</v>
+        <v>0.139849186092077</v>
       </c>
       <c r="J2">
-        <v>0.1821237474942176</v>
+        <v>0.1166736872995377</v>
       </c>
       <c r="K2">
-        <v>2195.02</v>
+        <v>1026.31</v>
       </c>
       <c r="L2">
-        <v>0.222305269447736</v>
+        <v>0.1086950996070789</v>
       </c>
       <c r="M2">
-        <v>1211.72</v>
+        <v>1149.239</v>
       </c>
       <c r="N2">
-        <v>0.0550551587517947</v>
+        <v>0.06719988539218094</v>
       </c>
       <c r="O2">
-        <v>0.5520314165702362</v>
+        <v>1.119777650027769</v>
       </c>
       <c r="P2">
-        <v>1112.74</v>
+        <v>991.0400000000001</v>
       </c>
       <c r="Q2">
-        <v>0.05055794849426604</v>
+        <v>0.05794945561285948</v>
       </c>
       <c r="R2">
-        <v>0.506938433362794</v>
+        <v>0.9656341651158034</v>
       </c>
       <c r="S2">
-        <v>98.97999999999995</v>
+        <v>158.199</v>
       </c>
       <c r="T2">
-        <v>0.08168553791304918</v>
+        <v>0.1376554398171312</v>
       </c>
       <c r="U2">
-        <v>2219.2</v>
+        <v>2187.6</v>
       </c>
       <c r="V2">
-        <v>0.10083056176508</v>
+        <v>0.1279163596814371</v>
       </c>
       <c r="W2">
-        <v>0.1450222882615156</v>
+        <v>0.08508655779510568</v>
       </c>
       <c r="X2">
-        <v>0.05497635683918478</v>
+        <v>0.09118679224338155</v>
       </c>
       <c r="Y2">
-        <v>0.0900459314223308</v>
+        <v>-0.006100234448275871</v>
       </c>
       <c r="Z2">
-        <v>1.455374785649158</v>
+        <v>1.127833873573814</v>
       </c>
       <c r="AA2">
-        <v>0.5013672875963729</v>
+        <v>0.1634520023255019</v>
       </c>
       <c r="AB2">
-        <v>0.05278883774660411</v>
+        <v>0.0859001045745989</v>
       </c>
       <c r="AC2">
-        <v>0.4486345136165704</v>
+        <v>0.07655508094256393</v>
       </c>
       <c r="AD2">
-        <v>2460.489</v>
+        <v>2360.982</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>2460.489</v>
+        <v>2360.982</v>
       </c>
       <c r="AG2">
-        <v>241.2890000000002</v>
+        <v>173.3820000000001</v>
       </c>
       <c r="AH2">
-        <v>0.1005525243904816</v>
+        <v>0.1213075294169148</v>
       </c>
       <c r="AI2">
-        <v>0.2194496493918306</v>
+        <v>0.2550680716080171</v>
       </c>
       <c r="AJ2">
-        <v>0.01084421110924799</v>
+        <v>0.0100364789210325</v>
       </c>
       <c r="AK2">
-        <v>0.02683108842998064</v>
+        <v>0.02452819351613215</v>
       </c>
       <c r="AL2">
-        <v>121.883</v>
+        <v>103.149</v>
       </c>
       <c r="AM2">
-        <v>121.883</v>
+        <v>103.149</v>
       </c>
       <c r="AN2">
-        <v>1.034514379414733</v>
+        <v>1.62969083266033</v>
       </c>
       <c r="AO2">
-        <v>18.30690088035247</v>
+        <v>12.80157829935336</v>
       </c>
       <c r="AP2">
-        <v>0.1014501345442315</v>
+        <v>0.1196786150628482</v>
       </c>
       <c r="AQ2">
-        <v>18.30690088035247</v>
+        <v>12.80157829935336</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Personal Group Holdings Plc (AIM:PGH)</t>
+          <t>Admiral Group plc (LSE:ADM)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -725,121 +725,124 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0506</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E3">
-        <v>-0.0622</v>
+        <v>0.114</v>
+      </c>
+      <c r="F3">
+        <v>-0.181</v>
       </c>
       <c r="G3">
-        <v>0.124157844080847</v>
+        <v>0.5605513255154783</v>
       </c>
       <c r="H3">
-        <v>0.124157844080847</v>
+        <v>0.5605513255154783</v>
       </c>
       <c r="I3">
-        <v>0.1029836381135707</v>
+        <v>0.3393541932973935</v>
       </c>
       <c r="J3">
-        <v>0.0825830698015491</v>
+        <v>0.2739023528097823</v>
       </c>
       <c r="K3">
-        <v>8.42</v>
+        <v>475.4</v>
       </c>
       <c r="L3">
-        <v>0.08103946102021174</v>
+        <v>0.2642138609459234</v>
       </c>
       <c r="M3">
-        <v>4.79</v>
+        <v>494.1</v>
       </c>
       <c r="N3">
-        <v>0.03496350364963504</v>
+        <v>0.06336565096952909</v>
       </c>
       <c r="O3">
-        <v>0.5688836104513064</v>
+        <v>1.039335296592343</v>
       </c>
       <c r="P3">
-        <v>4.74</v>
+        <v>494.1</v>
       </c>
       <c r="Q3">
-        <v>0.0345985401459854</v>
+        <v>0.06336565096952909</v>
       </c>
       <c r="R3">
-        <v>0.5629453681710214</v>
+        <v>1.039335296592343</v>
       </c>
       <c r="S3">
-        <v>0.04999999999999982</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>0.01043841336116907</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>26.9</v>
+        <v>615.6</v>
       </c>
       <c r="V3">
-        <v>0.1963503649635036</v>
+        <v>0.07894736842105263</v>
       </c>
       <c r="W3">
-        <v>0.1736082474226804</v>
+        <v>0.2063009894115605</v>
       </c>
       <c r="X3">
-        <v>0.05281028703201481</v>
+        <v>0.09245396815897303</v>
       </c>
       <c r="Y3">
-        <v>0.1207979603906656</v>
+        <v>0.1138470212525874</v>
       </c>
       <c r="Z3">
-        <v>7.846246790515026</v>
+        <v>0.6951935708214203</v>
       </c>
       <c r="AA3">
-        <v>0.6479671463812829</v>
+        <v>0.190415154706221</v>
       </c>
       <c r="AB3">
-        <v>0.05273430165168805</v>
+        <v>0.08563153789782472</v>
       </c>
       <c r="AC3">
-        <v>0.5952328447295949</v>
+        <v>0.1047836168083963</v>
       </c>
       <c r="AD3">
-        <v>0.351</v>
+        <v>1191.3</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.351</v>
+        <v>1191.3</v>
       </c>
       <c r="AG3">
-        <v>-26.549</v>
+        <v>575.6999999999999</v>
       </c>
       <c r="AH3">
-        <v>0.002555496501663621</v>
+        <v>0.1325301204819277</v>
       </c>
       <c r="AI3">
-        <v>0.006025647628366895</v>
+        <v>0.4627306273062731</v>
       </c>
       <c r="AJ3">
-        <v>-0.2403690324216168</v>
+        <v>0.06875425459496254</v>
       </c>
       <c r="AK3">
-        <v>-0.8468310420720232</v>
+        <v>0.2938894277400582</v>
       </c>
       <c r="AL3">
-        <v>0.064</v>
+        <v>26.4</v>
       </c>
       <c r="AM3">
-        <v>0.064</v>
+        <v>26.4</v>
       </c>
       <c r="AN3">
-        <v>0.03133928571428572</v>
+        <v>1.912199036918138</v>
       </c>
       <c r="AO3">
-        <v>167.1875</v>
+        <v>23.12878787878788</v>
       </c>
       <c r="AP3">
-        <v>-2.370446428571429</v>
+        <v>0.9240770465489565</v>
       </c>
       <c r="AQ3">
-        <v>167.1875</v>
+        <v>23.12878787878788</v>
       </c>
     </row>
     <row r="4">
@@ -850,7 +853,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Admiral Group plc (LSE:ADM)</t>
+          <t>Sabre Insurance Group plc (LSE:SBRE)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -858,125 +861,119 @@
           <t>Insurance (Prop/Cas.)</t>
         </is>
       </c>
-      <c r="D4">
-        <v>0.0891</v>
-      </c>
-      <c r="E4">
-        <v>0.291</v>
-      </c>
       <c r="F4">
-        <v>-0.057</v>
+        <v>0.21</v>
       </c>
       <c r="G4">
-        <v>0.4266478021173831</v>
+        <v>0.2645060115002614</v>
       </c>
       <c r="H4">
-        <v>0.4266478021173831</v>
+        <v>0.2645060115002614</v>
       </c>
       <c r="I4">
-        <v>0.5619846806849784</v>
+        <v>0.123366440146367</v>
       </c>
       <c r="J4">
-        <v>0.4558708030898024</v>
+        <v>0.09932043910088867</v>
       </c>
       <c r="K4">
-        <v>1509.1</v>
+        <v>19</v>
       </c>
       <c r="L4">
-        <v>0.7362540859637996</v>
+        <v>0.09932043910088866</v>
       </c>
       <c r="M4">
-        <v>627.6</v>
+        <v>25.338</v>
       </c>
       <c r="N4">
-        <v>0.05040963855421687</v>
+        <v>0.07932999373825925</v>
       </c>
       <c r="O4">
-        <v>0.4158770127890796</v>
+        <v>1.333578947368421</v>
       </c>
       <c r="P4">
-        <v>627.6</v>
+        <v>24.5</v>
       </c>
       <c r="Q4">
-        <v>0.05040963855421687</v>
+        <v>0.07670632435817158</v>
       </c>
       <c r="R4">
-        <v>0.4158770127890796</v>
+        <v>1.289473684210526</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>0.838000000000001</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>0.0330728550003947</v>
       </c>
       <c r="U4">
-        <v>546.8</v>
+        <v>33.8</v>
       </c>
       <c r="V4">
-        <v>0.04391967871485943</v>
+        <v>0.1058234189104571</v>
       </c>
       <c r="W4">
-        <v>1.172298609492737</v>
+        <v>0.05450372920252438</v>
       </c>
       <c r="X4">
-        <v>0.05497635683918478</v>
+        <v>0.08694639126324294</v>
       </c>
       <c r="Y4">
-        <v>1.117322252653552</v>
+        <v>-0.03244266206071856</v>
       </c>
       <c r="Z4">
-        <v>1.215141095565568</v>
+        <v>1.921879081355864</v>
       </c>
       <c r="AA4">
-        <v>0.5539473471028977</v>
+        <v>0.190881874259077</v>
       </c>
       <c r="AB4">
-        <v>0.05278883774660411</v>
+        <v>0.08693720647918093</v>
       </c>
       <c r="AC4">
-        <v>0.5011585093562936</v>
+        <v>0.103944667779896</v>
       </c>
       <c r="AD4">
-        <v>916.6</v>
+        <v>0.073</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>916.6</v>
+        <v>0.073</v>
       </c>
       <c r="AG4">
-        <v>369.8000000000001</v>
+        <v>-33.727</v>
       </c>
       <c r="AH4">
-        <v>0.06857390809929227</v>
+        <v>0.0002285013131000116</v>
       </c>
       <c r="AI4">
-        <v>0.2841465682931366</v>
+        <v>0.0002649987476086586</v>
       </c>
       <c r="AJ4">
-        <v>0.02884600383781339</v>
+        <v>-0.1180615598954049</v>
       </c>
       <c r="AK4">
-        <v>0.1380365808137365</v>
+        <v>-0.1395563426613647</v>
       </c>
       <c r="AL4">
-        <v>27.6</v>
+        <v>0.015</v>
       </c>
       <c r="AM4">
-        <v>27.6</v>
+        <v>0.015</v>
       </c>
       <c r="AN4">
-        <v>0.7833518502692078</v>
+        <v>0.003080168776371308</v>
       </c>
       <c r="AO4">
-        <v>41.73550724637681</v>
+        <v>1573.333333333333</v>
       </c>
       <c r="AP4">
-        <v>0.3160413639859842</v>
+        <v>-1.423080168776371</v>
       </c>
       <c r="AQ4">
-        <v>41.73550724637681</v>
+        <v>1573.333333333333</v>
       </c>
     </row>
     <row r="5">
@@ -987,7 +984,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sabre Insurance Group plc (LSE:SBRE)</t>
+          <t>Personal Group Holdings Plc (AIM:PGH)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -995,119 +992,122 @@
           <t>Insurance (Prop/Cas.)</t>
         </is>
       </c>
-      <c r="F5">
-        <v>0.08</v>
+      <c r="D5">
+        <v>0.07389999999999999</v>
+      </c>
+      <c r="E5">
+        <v>-0.292</v>
       </c>
       <c r="G5">
-        <v>0.3018360949395432</v>
+        <v>0.07596982758620689</v>
       </c>
       <c r="H5">
-        <v>0.3018360949395432</v>
+        <v>0.07596982758620689</v>
       </c>
       <c r="I5">
-        <v>0.2695924764890282</v>
+        <v>0.02553879310344828</v>
       </c>
       <c r="J5">
-        <v>0.2184551348588299</v>
+        <v>0.02439626814882033</v>
       </c>
       <c r="K5">
-        <v>48.8</v>
+        <v>1.81</v>
       </c>
       <c r="L5">
-        <v>0.2185400806090461</v>
+        <v>0.01950431034482759</v>
       </c>
       <c r="M5">
-        <v>47.03</v>
+        <v>4.001</v>
       </c>
       <c r="N5">
-        <v>0.07587931590835754</v>
+        <v>0.05436141304347827</v>
       </c>
       <c r="O5">
-        <v>0.9637295081967214</v>
+        <v>2.210497237569061</v>
       </c>
       <c r="P5">
-        <v>44.1</v>
+        <v>3.94</v>
       </c>
       <c r="Q5">
-        <v>0.07115198451113264</v>
+        <v>0.05353260869565218</v>
       </c>
       <c r="R5">
-        <v>0.903688524590164</v>
+        <v>2.176795580110497</v>
       </c>
       <c r="S5">
-        <v>2.93</v>
+        <v>0.06100000000000039</v>
       </c>
       <c r="T5">
-        <v>0.06230065915373165</v>
+        <v>0.01524618845288687</v>
       </c>
       <c r="U5">
-        <v>33.7</v>
+        <v>24.4</v>
       </c>
       <c r="V5">
-        <v>0.05437237818651178</v>
+        <v>0.3315217391304348</v>
       </c>
       <c r="W5">
-        <v>0.1450222882615156</v>
+        <v>0.03126079447322971</v>
       </c>
       <c r="X5">
-        <v>0.05275373168176629</v>
+        <v>0.08708971593199419</v>
       </c>
       <c r="Y5">
-        <v>0.09226855657974929</v>
+        <v>-0.05582892145876448</v>
       </c>
       <c r="Z5">
-        <v>2.295058378556159</v>
+        <v>6.69987726517941</v>
       </c>
       <c r="AA5">
-        <v>0.5013672875963729</v>
+        <v>0.1634520023255019</v>
       </c>
       <c r="AB5">
-        <v>0.05273277397980258</v>
+        <v>0.08689692138293796</v>
       </c>
       <c r="AC5">
-        <v>0.4486345136165704</v>
+        <v>0.07655508094256393</v>
       </c>
       <c r="AD5">
-        <v>0.438</v>
+        <v>0.309</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>0.438</v>
+        <v>0.309</v>
       </c>
       <c r="AG5">
-        <v>-33.262</v>
+        <v>-24.091</v>
       </c>
       <c r="AH5">
-        <v>0.0007061805306995058</v>
+        <v>0.004180816950574356</v>
       </c>
       <c r="AI5">
-        <v>0.001254877692400254</v>
+        <v>0.006266604473828308</v>
       </c>
       <c r="AJ5">
-        <v>-0.056709028230055</v>
+        <v>-0.4865983962511866</v>
       </c>
       <c r="AK5">
-        <v>-0.105480468576575</v>
+        <v>-0.9671604640892848</v>
       </c>
       <c r="AL5">
-        <v>0.019</v>
+        <v>0.034</v>
       </c>
       <c r="AM5">
-        <v>0.019</v>
+        <v>0.034</v>
       </c>
       <c r="AN5">
-        <v>0.007239669421487603</v>
+        <v>0.1091872791519435</v>
       </c>
       <c r="AO5">
-        <v>3168.421052631579</v>
+        <v>69.70588235294117</v>
       </c>
       <c r="AP5">
-        <v>-0.5497851239669421</v>
+        <v>-8.512720848056537</v>
       </c>
       <c r="AQ5">
-        <v>3168.421052631579</v>
+        <v>69.70588235294117</v>
       </c>
     </row>
     <row r="6">
@@ -1127,124 +1127,124 @@
         </is>
       </c>
       <c r="D6">
-        <v>-0.00343</v>
+        <v>-0.0109</v>
       </c>
       <c r="E6">
-        <v>-0.00526</v>
+        <v>-0.0215</v>
       </c>
       <c r="F6">
-        <v>0.0534</v>
+        <v>0.0897</v>
       </c>
       <c r="G6">
-        <v>0.1858748645720477</v>
+        <v>0.2176822105316921</v>
       </c>
       <c r="H6">
-        <v>0.1858748645720477</v>
+        <v>0.2176822105316921</v>
       </c>
       <c r="I6">
-        <v>0.1945196821957385</v>
+        <v>0.1123652893406201</v>
       </c>
       <c r="J6">
-        <v>0.1545393522582745</v>
+        <v>0.08845994994359088</v>
       </c>
       <c r="K6">
-        <v>522.6</v>
+        <v>347</v>
       </c>
       <c r="L6">
-        <v>0.1179577464788732</v>
+        <v>0.08861535318453445</v>
       </c>
       <c r="M6">
-        <v>532.3</v>
+        <v>505</v>
       </c>
       <c r="N6">
-        <v>0.1069090178750753</v>
+        <v>0.1457768027250159</v>
       </c>
       <c r="O6">
-        <v>1.018561040949101</v>
+        <v>1.455331412103746</v>
       </c>
       <c r="P6">
-        <v>436.3</v>
+        <v>365.5</v>
       </c>
       <c r="Q6">
-        <v>0.08762803775858606</v>
+        <v>0.1055077651405808</v>
       </c>
       <c r="R6">
-        <v>0.8348641408342901</v>
+        <v>1.053314121037464</v>
       </c>
       <c r="S6">
-        <v>95.99999999999994</v>
+        <v>139.5</v>
       </c>
       <c r="T6">
-        <v>0.1803494270148412</v>
+        <v>0.2762376237623763</v>
       </c>
       <c r="U6">
-        <v>1187.1</v>
+        <v>944.4</v>
       </c>
       <c r="V6">
-        <v>0.2384213697529624</v>
+        <v>0.2726170544425842</v>
       </c>
       <c r="W6">
-        <v>0.1360193644100882</v>
+        <v>0.08508655779510568</v>
       </c>
       <c r="X6">
-        <v>0.05825496212672526</v>
+        <v>0.09244403838808904</v>
       </c>
       <c r="Y6">
-        <v>0.07776440228336298</v>
+        <v>-0.007357480592983356</v>
       </c>
       <c r="Z6">
-        <v>1.528145695364238</v>
+        <v>1.119983983067814</v>
       </c>
       <c r="AA6">
-        <v>0.2361586459178599</v>
+        <v>0.0990737270798024</v>
       </c>
       <c r="AB6">
-        <v>0.05285890184597485</v>
+        <v>0.08563357883550687</v>
       </c>
       <c r="AC6">
-        <v>0.183299744071885</v>
+        <v>0.01344014824429553</v>
       </c>
       <c r="AD6">
-        <v>902.1</v>
+        <v>528.3</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>902.1</v>
+        <v>528.3</v>
       </c>
       <c r="AG6">
-        <v>-284.9999999999999</v>
+        <v>-416.1</v>
       </c>
       <c r="AH6">
-        <v>0.153389672000136</v>
+        <v>0.1323231058234189</v>
       </c>
       <c r="AI6">
-        <v>0.1811336666465876</v>
+        <v>0.1427105000135066</v>
       </c>
       <c r="AJ6">
-        <v>-0.06071580741371962</v>
+        <v>-0.1365112693153112</v>
       </c>
       <c r="AK6">
-        <v>-0.0751344511230623</v>
+        <v>-0.1508975521305531</v>
       </c>
       <c r="AL6">
-        <v>51.7</v>
+        <v>39.5</v>
       </c>
       <c r="AM6">
-        <v>51.7</v>
+        <v>39.5</v>
       </c>
       <c r="AN6">
-        <v>0.9247565351102</v>
+        <v>0.9682917888563048</v>
       </c>
       <c r="AO6">
-        <v>16.66924564796905</v>
+        <v>11.13924050632911</v>
       </c>
       <c r="AP6">
-        <v>-0.2921578677601229</v>
+        <v>-0.7626466275659824</v>
       </c>
       <c r="AQ6">
-        <v>16.66924564796905</v>
+        <v>11.13924050632911</v>
       </c>
     </row>
     <row r="7">
@@ -1264,79 +1264,82 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.111</v>
+        <v>0.122</v>
       </c>
       <c r="E7">
-        <v>-0.154</v>
+        <v>-0.0643</v>
       </c>
       <c r="F7">
-        <v>0.2</v>
+        <v>0.65</v>
       </c>
       <c r="G7">
-        <v>-0.003195721646122742</v>
+        <v>0.1085712625983909</v>
       </c>
       <c r="H7">
-        <v>-0.003195721646122742</v>
+        <v>0.1085712625983909</v>
       </c>
       <c r="I7">
-        <v>0.04783799647818431</v>
+        <v>0.07084144180777832</v>
       </c>
       <c r="J7">
-        <v>0.0388340583499262</v>
+        <v>0.05785489739074135</v>
       </c>
       <c r="K7">
-        <v>106.1</v>
+        <v>183.1</v>
       </c>
       <c r="L7">
-        <v>0.03459857822996152</v>
+        <v>0.05318191059862325</v>
       </c>
       <c r="M7">
-        <v>-0</v>
+        <v>120.8</v>
       </c>
       <c r="N7">
-        <v>-0</v>
+        <v>0.02217734532770332</v>
       </c>
       <c r="O7">
-        <v>-0</v>
+        <v>0.6597487711632988</v>
       </c>
       <c r="P7">
-        <v>-0</v>
+        <v>103</v>
       </c>
       <c r="Q7">
-        <v>-0</v>
+        <v>0.01890949146319075</v>
       </c>
       <c r="R7">
-        <v>-0</v>
+        <v>0.5625341343528127</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>17.8</v>
+      </c>
+      <c r="T7">
+        <v>0.1473509933774834</v>
       </c>
       <c r="U7">
-        <v>424.7</v>
+        <v>569.4</v>
       </c>
       <c r="V7">
-        <v>0.1110791442171889</v>
+        <v>0.1045346062052506</v>
       </c>
       <c r="W7">
-        <v>0.05805427883563143</v>
+        <v>0.09352811973233896</v>
       </c>
       <c r="X7">
-        <v>0.05784256612407385</v>
+        <v>0.09118679224338155</v>
       </c>
       <c r="Y7">
-        <v>0.0002117127115575726</v>
+        <v>0.002341327488957406</v>
       </c>
       <c r="Z7">
-        <v>1.468748503280809</v>
+        <v>1.583670653173873</v>
       </c>
       <c r="AA7">
-        <v>0.05703746507777369</v>
+        <v>0.09162310314010276</v>
       </c>
       <c r="AB7">
-        <v>0.05285079859868504</v>
+        <v>0.0859001045745989</v>
       </c>
       <c r="AC7">
-        <v>0.004186666479088656</v>
+        <v>0.005722998565503859</v>
       </c>
       <c r="AD7">
         <v>641</v>
@@ -1348,37 +1351,37 @@
         <v>641</v>
       </c>
       <c r="AG7">
-        <v>216.3</v>
+        <v>71.60000000000002</v>
       </c>
       <c r="AH7">
-        <v>0.1435803243436968</v>
+        <v>0.1052890932982917</v>
       </c>
       <c r="AI7">
-        <v>0.2466617924346789</v>
+        <v>0.2414221686565478</v>
       </c>
       <c r="AJ7">
-        <v>0.05354357996880956</v>
+        <v>0.0129743050773747</v>
       </c>
       <c r="AK7">
-        <v>0.09949402023919043</v>
+        <v>0.03432900225344011</v>
       </c>
       <c r="AL7">
-        <v>42.5</v>
+        <v>37.2</v>
       </c>
       <c r="AM7">
-        <v>42.5</v>
+        <v>37.2</v>
       </c>
       <c r="AN7">
-        <v>3.978895096213532</v>
+        <v>2.527602523659306</v>
       </c>
       <c r="AO7">
-        <v>3.451764705882353</v>
+        <v>6.556451612903225</v>
       </c>
       <c r="AP7">
-        <v>1.342644320297952</v>
+        <v>0.2823343848580442</v>
       </c>
       <c r="AQ7">
-        <v>3.451764705882353</v>
+        <v>6.556451612903225</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/united_kingdom/united_kingdom_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/united_kingdom/united_kingdom_insurance_prop_cas.xlsx
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.07195</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="E2">
-        <v>-0.04289999999999999</v>
+        <v>0.009519999999999999</v>
       </c>
       <c r="F2">
-        <v>0.14985</v>
+        <v>0.07844999999999999</v>
       </c>
       <c r="G2">
-        <v>0.2427902691138624</v>
+        <v>0.102483019708273</v>
       </c>
       <c r="H2">
-        <v>0.2427902691138624</v>
+        <v>0.102483019708273</v>
       </c>
       <c r="I2">
-        <v>0.139849186092077</v>
+        <v>0.08683609843001894</v>
       </c>
       <c r="J2">
-        <v>0.1166736872995377</v>
+        <v>0.0754398944677675</v>
       </c>
       <c r="K2">
-        <v>1026.31</v>
+        <v>493.2</v>
       </c>
       <c r="L2">
-        <v>0.1086950996070789</v>
+        <v>0.04576327803139962</v>
       </c>
       <c r="M2">
-        <v>1149.239</v>
+        <v>878.1608</v>
       </c>
       <c r="N2">
-        <v>0.06719988539218094</v>
+        <v>0.04839071377009252</v>
       </c>
       <c r="O2">
-        <v>1.119777650027769</v>
+        <v>1.780536901865369</v>
       </c>
       <c r="P2">
-        <v>991.0400000000001</v>
+        <v>833.3138</v>
       </c>
       <c r="Q2">
-        <v>0.05794945561285948</v>
+        <v>0.04591943705124178</v>
       </c>
       <c r="R2">
-        <v>0.9656341651158034</v>
+        <v>1.689606244931062</v>
       </c>
       <c r="S2">
-        <v>158.199</v>
+        <v>44.84700000000002</v>
       </c>
       <c r="T2">
-        <v>0.1376554398171312</v>
+        <v>0.05106923470052412</v>
       </c>
       <c r="U2">
-        <v>2187.6</v>
+        <v>3264.1</v>
       </c>
       <c r="V2">
-        <v>0.1279163596814371</v>
+        <v>0.1798669774567015</v>
       </c>
       <c r="W2">
-        <v>0.08508655779510568</v>
+        <v>0.03340595497458242</v>
       </c>
       <c r="X2">
-        <v>0.09118679224338155</v>
+        <v>0.07888619168113273</v>
       </c>
       <c r="Y2">
-        <v>-0.006100234448275871</v>
+        <v>-0.0454802367065503</v>
       </c>
       <c r="Z2">
-        <v>1.127833873573814</v>
+        <v>1.651809293059587</v>
       </c>
       <c r="AA2">
-        <v>0.1634520023255019</v>
+        <v>0.1844792358615664</v>
       </c>
       <c r="AB2">
-        <v>0.0859001045745989</v>
+        <v>0.07419220929811585</v>
       </c>
       <c r="AC2">
-        <v>0.07655508094256393</v>
+        <v>0.1095151617392768</v>
       </c>
       <c r="AD2">
-        <v>2360.982</v>
+        <v>2828.763</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>2360.982</v>
+        <v>2828.763</v>
       </c>
       <c r="AG2">
-        <v>173.3820000000001</v>
+        <v>-435.337</v>
       </c>
       <c r="AH2">
-        <v>0.1213075294169148</v>
+        <v>0.1348567173925822</v>
       </c>
       <c r="AI2">
-        <v>0.2550680716080171</v>
+        <v>0.2780421753271102</v>
       </c>
       <c r="AJ2">
-        <v>0.0100364789210325</v>
+        <v>-0.02457869858919647</v>
       </c>
       <c r="AK2">
-        <v>0.02452819351613215</v>
+        <v>-0.06300317391493745</v>
       </c>
       <c r="AL2">
-        <v>103.149</v>
+        <v>131.738</v>
       </c>
       <c r="AM2">
-        <v>103.149</v>
+        <v>131.738</v>
       </c>
       <c r="AN2">
-        <v>1.62969083266033</v>
+        <v>2.632044029253587</v>
       </c>
       <c r="AO2">
-        <v>12.80157829935336</v>
+        <v>7.103872838512806</v>
       </c>
       <c r="AP2">
-        <v>0.1196786150628482</v>
+        <v>-0.4050626197964159</v>
       </c>
       <c r="AQ2">
-        <v>12.80157829935336</v>
+        <v>7.103872838512806</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Admiral Group plc (LSE:ADM)</t>
+          <t>Personal Group Holdings Plc (AIM:PGH)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -725,124 +725,118 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="E3">
-        <v>0.114</v>
-      </c>
-      <c r="F3">
-        <v>-0.181</v>
+        <v>0.161</v>
       </c>
       <c r="G3">
-        <v>0.5605513255154783</v>
+        <v>0.04784</v>
       </c>
       <c r="H3">
-        <v>0.5605513255154783</v>
+        <v>0.04784</v>
       </c>
       <c r="I3">
-        <v>0.3393541932973935</v>
+        <v>0.05088</v>
       </c>
       <c r="J3">
-        <v>0.2739023528097823</v>
+        <v>0.05088</v>
       </c>
       <c r="K3">
-        <v>475.4</v>
+        <v>-8.1</v>
       </c>
       <c r="L3">
-        <v>0.2642138609459234</v>
+        <v>-0.0648</v>
       </c>
       <c r="M3">
-        <v>494.1</v>
+        <v>4.247</v>
       </c>
       <c r="N3">
-        <v>0.06336565096952909</v>
+        <v>0.05786103542234332</v>
       </c>
       <c r="O3">
-        <v>1.039335296592343</v>
+        <v>-0.524320987654321</v>
       </c>
       <c r="P3">
-        <v>494.1</v>
+        <v>4.21</v>
       </c>
       <c r="Q3">
-        <v>0.06336565096952909</v>
+        <v>0.05735694822888283</v>
       </c>
       <c r="R3">
-        <v>1.039335296592343</v>
+        <v>-0.5197530864197532</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>0.03699999999999992</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>0.008712032022604174</v>
       </c>
       <c r="U3">
-        <v>615.6</v>
+        <v>26.5</v>
       </c>
       <c r="V3">
-        <v>0.07894736842105263</v>
+        <v>0.3610354223433242</v>
       </c>
       <c r="W3">
-        <v>0.2063009894115605</v>
+        <v>-0.1653061224489796</v>
       </c>
       <c r="X3">
-        <v>0.09245396815897303</v>
+        <v>0.0752090684800186</v>
       </c>
       <c r="Y3">
-        <v>0.1138470212525874</v>
+        <v>-0.2405151909289982</v>
       </c>
       <c r="Z3">
-        <v>0.6951935708214203</v>
+        <v>13.14544116100537</v>
       </c>
       <c r="AA3">
-        <v>0.190415154706221</v>
+        <v>0.668840046271953</v>
       </c>
       <c r="AB3">
-        <v>0.08563153789782472</v>
+        <v>0.07488206579644836</v>
       </c>
       <c r="AC3">
-        <v>0.1047836168083963</v>
+        <v>0.5939579804755046</v>
       </c>
       <c r="AD3">
-        <v>1191.3</v>
+        <v>0.663</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1191.3</v>
+        <v>0.663</v>
       </c>
       <c r="AG3">
-        <v>575.6999999999999</v>
+        <v>-25.837</v>
       </c>
       <c r="AH3">
-        <v>0.1325301204819277</v>
+        <v>0.008951838299825824</v>
       </c>
       <c r="AI3">
-        <v>0.4627306273062731</v>
+        <v>0.01663196447833831</v>
       </c>
       <c r="AJ3">
-        <v>0.06875425459496254</v>
+        <v>-0.5432163656623846</v>
       </c>
       <c r="AK3">
-        <v>0.2938894277400582</v>
+        <v>-1.933473022524882</v>
       </c>
       <c r="AL3">
-        <v>26.4</v>
+        <v>0.037</v>
       </c>
       <c r="AM3">
-        <v>26.4</v>
+        <v>0.037</v>
       </c>
       <c r="AN3">
-        <v>1.912199036918138</v>
+        <v>0.09692982456140352</v>
       </c>
       <c r="AO3">
-        <v>23.12878787878788</v>
+        <v>171.8918918918919</v>
       </c>
       <c r="AP3">
-        <v>0.9240770465489565</v>
+        <v>-3.77733918128655</v>
       </c>
       <c r="AQ3">
-        <v>23.12878787878788</v>
+        <v>171.8918918918919</v>
       </c>
     </row>
     <row r="4">
@@ -853,7 +847,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Sabre Insurance Group plc (LSE:SBRE)</t>
+          <t>Admiral Group plc (LSE:ADM)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -861,119 +855,125 @@
           <t>Insurance (Prop/Cas.)</t>
         </is>
       </c>
+      <c r="D4">
+        <v>0.08210000000000001</v>
+      </c>
+      <c r="E4">
+        <v>0.009519999999999999</v>
+      </c>
       <c r="F4">
-        <v>0.21</v>
+        <v>0.08689999999999999</v>
       </c>
       <c r="G4">
-        <v>0.2645060115002614</v>
+        <v>0.2732471743144054</v>
       </c>
       <c r="H4">
-        <v>0.2645060115002614</v>
+        <v>0.2732471743144054</v>
       </c>
       <c r="I4">
-        <v>0.123366440146367</v>
+        <v>0.3070653397577341</v>
       </c>
       <c r="J4">
-        <v>0.09932043910088867</v>
+        <v>0.2336586371141033</v>
       </c>
       <c r="K4">
-        <v>19</v>
+        <v>464</v>
       </c>
       <c r="L4">
-        <v>0.09932043910088866</v>
+        <v>0.2089431260413383</v>
       </c>
       <c r="M4">
-        <v>25.338</v>
+        <v>587.4</v>
       </c>
       <c r="N4">
-        <v>0.07932999373825925</v>
+        <v>0.05770987866581519</v>
       </c>
       <c r="O4">
-        <v>1.333578947368421</v>
+        <v>1.265948275862069</v>
       </c>
       <c r="P4">
-        <v>24.5</v>
+        <v>587.4</v>
       </c>
       <c r="Q4">
-        <v>0.07670632435817158</v>
+        <v>0.05770987866581519</v>
       </c>
       <c r="R4">
-        <v>1.289473684210526</v>
+        <v>1.265948275862069</v>
       </c>
       <c r="S4">
-        <v>0.838000000000001</v>
+        <v>0</v>
       </c>
       <c r="T4">
-        <v>0.0330728550003947</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>33.8</v>
+        <v>588</v>
       </c>
       <c r="V4">
-        <v>0.1058234189104571</v>
+        <v>0.0577688264479049</v>
       </c>
       <c r="W4">
-        <v>0.05450372920252438</v>
+        <v>0.3359154419749512</v>
       </c>
       <c r="X4">
-        <v>0.08694639126324294</v>
+        <v>0.07926629677325266</v>
       </c>
       <c r="Y4">
-        <v>-0.03244266206071856</v>
+        <v>0.2566491452016985</v>
       </c>
       <c r="Z4">
-        <v>1.921879081355864</v>
+        <v>1.180407165258066</v>
       </c>
       <c r="AA4">
-        <v>0.190881874259077</v>
+        <v>0.2758123294739219</v>
       </c>
       <c r="AB4">
-        <v>0.08693720647918093</v>
+        <v>0.07370989528558659</v>
       </c>
       <c r="AC4">
-        <v>0.103944667779896</v>
+        <v>0.2021024341883353</v>
       </c>
       <c r="AD4">
-        <v>0.073</v>
+        <v>1614.5</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.073</v>
+        <v>1614.5</v>
       </c>
       <c r="AG4">
-        <v>-33.727</v>
+        <v>1026.5</v>
       </c>
       <c r="AH4">
-        <v>0.0002285013131000116</v>
+        <v>0.1369032476893072</v>
       </c>
       <c r="AI4">
-        <v>0.0002649987476086586</v>
+        <v>0.5777213196879697</v>
       </c>
       <c r="AJ4">
-        <v>-0.1180615598954049</v>
+        <v>0.09161088799643016</v>
       </c>
       <c r="AK4">
-        <v>-0.1395563426613647</v>
+        <v>0.4651953231215445</v>
       </c>
       <c r="AL4">
-        <v>0.015</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="AM4">
-        <v>0.015</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="AN4">
-        <v>0.003080168776371308</v>
+        <v>2.363144028103044</v>
       </c>
       <c r="AO4">
-        <v>1573.333333333333</v>
+        <v>8.960578186596583</v>
       </c>
       <c r="AP4">
-        <v>-1.423080168776371</v>
+        <v>1.502488290398126</v>
       </c>
       <c r="AQ4">
-        <v>1573.333333333333</v>
+        <v>8.960578186596583</v>
       </c>
     </row>
     <row r="5">
@@ -984,7 +984,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Personal Group Holdings Plc (AIM:PGH)</t>
+          <t>Sabre Insurance Group plc (LSE:SBRE)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -993,121 +993,121 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.07389999999999999</v>
+        <v>-0.0466</v>
       </c>
       <c r="E5">
-        <v>-0.292</v>
+        <v>-0.315</v>
       </c>
       <c r="G5">
-        <v>0.07596982758620689</v>
+        <v>0.0797735460627895</v>
       </c>
       <c r="H5">
-        <v>0.07596982758620689</v>
+        <v>0.0797735460627895</v>
       </c>
       <c r="I5">
-        <v>0.02553879310344828</v>
+        <v>0.06124549665465774</v>
       </c>
       <c r="J5">
-        <v>0.02439626814882033</v>
+        <v>0.04915616818456443</v>
       </c>
       <c r="K5">
-        <v>1.81</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L5">
-        <v>0.01950431034482759</v>
+        <v>0.04734945959855892</v>
       </c>
       <c r="M5">
-        <v>4.001</v>
+        <v>9.313799999999999</v>
       </c>
       <c r="N5">
-        <v>0.05436141304347827</v>
+        <v>0.01943208846234091</v>
       </c>
       <c r="O5">
-        <v>2.210497237569061</v>
+        <v>1.012369565217391</v>
       </c>
       <c r="P5">
-        <v>3.94</v>
+        <v>8.203799999999999</v>
       </c>
       <c r="Q5">
-        <v>0.05353260869565218</v>
+        <v>0.01711621114124765</v>
       </c>
       <c r="R5">
-        <v>2.176795580110497</v>
+        <v>0.8917173913043478</v>
       </c>
       <c r="S5">
-        <v>0.06100000000000039</v>
+        <v>1.109999999999999</v>
       </c>
       <c r="T5">
-        <v>0.01524618845288687</v>
+        <v>0.1191779939444695</v>
       </c>
       <c r="U5">
-        <v>24.4</v>
+        <v>37.3</v>
       </c>
       <c r="V5">
-        <v>0.3315217391304348</v>
+        <v>0.07782182349259335</v>
       </c>
       <c r="W5">
-        <v>0.03126079447322971</v>
+        <v>0.03340595497458242</v>
       </c>
       <c r="X5">
-        <v>0.08708971593199419</v>
+        <v>0.0749640741222896</v>
       </c>
       <c r="Y5">
-        <v>-0.05582892145876448</v>
+        <v>-0.04155811914770718</v>
       </c>
       <c r="Z5">
-        <v>6.69987726517941</v>
+        <v>3.752921406910943</v>
       </c>
       <c r="AA5">
-        <v>0.1634520023255019</v>
+        <v>0.1844792358615664</v>
       </c>
       <c r="AB5">
-        <v>0.08689692138293796</v>
+        <v>0.0749640741222896</v>
       </c>
       <c r="AC5">
-        <v>0.07655508094256393</v>
+        <v>0.1095151617392768</v>
       </c>
       <c r="AD5">
-        <v>0.309</v>
+        <v>0</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>0.309</v>
+        <v>0</v>
       </c>
       <c r="AG5">
-        <v>-24.091</v>
+        <v>-37.3</v>
       </c>
       <c r="AH5">
-        <v>0.004180816950574356</v>
+        <v>0</v>
       </c>
       <c r="AI5">
-        <v>0.006266604473828308</v>
+        <v>0</v>
       </c>
       <c r="AJ5">
-        <v>-0.4865983962511866</v>
+        <v>-0.0843891402714932</v>
       </c>
       <c r="AK5">
-        <v>-0.9671604640892848</v>
+        <v>-0.1456462319406482</v>
       </c>
       <c r="AL5">
-        <v>0.034</v>
+        <v>0.001</v>
       </c>
       <c r="AM5">
-        <v>0.034</v>
+        <v>0.001</v>
       </c>
       <c r="AN5">
-        <v>0.1091872791519435</v>
+        <v>0</v>
       </c>
       <c r="AO5">
-        <v>69.70588235294117</v>
+        <v>11900</v>
       </c>
       <c r="AP5">
-        <v>-8.512720848056537</v>
+        <v>-3.082644628099173</v>
       </c>
       <c r="AQ5">
-        <v>69.70588235294117</v>
+        <v>11900</v>
       </c>
     </row>
     <row r="6">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Direct Line Insurance Group plc (LSE:DLG)</t>
+          <t>Beazley plc (LSE:BEZ)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1127,124 +1127,124 @@
         </is>
       </c>
       <c r="D6">
-        <v>-0.0109</v>
+        <v>0.135</v>
       </c>
       <c r="E6">
-        <v>-0.0215</v>
+        <v>0.276</v>
       </c>
       <c r="F6">
-        <v>0.0897</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G6">
-        <v>0.2176822105316921</v>
+        <v>0.06613770156130022</v>
       </c>
       <c r="H6">
-        <v>0.2176822105316921</v>
+        <v>0.06613770156130022</v>
       </c>
       <c r="I6">
-        <v>0.1123652893406201</v>
+        <v>0.05889429229587919</v>
       </c>
       <c r="J6">
-        <v>0.08845994994359088</v>
+        <v>0.04595284520956391</v>
       </c>
       <c r="K6">
-        <v>347</v>
+        <v>150.2</v>
       </c>
       <c r="L6">
-        <v>0.08861535318453445</v>
+        <v>0.03844381878679293</v>
       </c>
       <c r="M6">
-        <v>505</v>
+        <v>134.9</v>
       </c>
       <c r="N6">
-        <v>0.1457768027250159</v>
+        <v>0.03061386587995008</v>
       </c>
       <c r="O6">
-        <v>1.455331412103746</v>
+        <v>0.8981358189081227</v>
       </c>
       <c r="P6">
-        <v>365.5</v>
+        <v>107.7</v>
       </c>
       <c r="Q6">
-        <v>0.1055077651405808</v>
+        <v>0.02444116645864065</v>
       </c>
       <c r="R6">
-        <v>1.053314121037464</v>
+        <v>0.7170439414114514</v>
       </c>
       <c r="S6">
-        <v>139.5</v>
+        <v>27.2</v>
       </c>
       <c r="T6">
-        <v>0.2762376237623763</v>
+        <v>0.2016308376575241</v>
       </c>
       <c r="U6">
-        <v>944.4</v>
+        <v>577.9</v>
       </c>
       <c r="V6">
-        <v>0.2726170544425842</v>
+        <v>0.1311471689549529</v>
       </c>
       <c r="W6">
-        <v>0.08508655779510568</v>
+        <v>0.07457425152673651</v>
       </c>
       <c r="X6">
-        <v>0.09244403838808904</v>
+        <v>0.07888619168113273</v>
       </c>
       <c r="Y6">
-        <v>-0.007357480592983356</v>
+        <v>-0.004311940154396218</v>
       </c>
       <c r="Z6">
-        <v>1.119983983067814</v>
+        <v>1.873232008438414</v>
       </c>
       <c r="AA6">
-        <v>0.0990737270798024</v>
+        <v>0.08608034052537096</v>
       </c>
       <c r="AB6">
-        <v>0.08563357883550687</v>
+        <v>0.07380670407760948</v>
       </c>
       <c r="AC6">
-        <v>0.01344014824429553</v>
+        <v>0.01227363644776149</v>
       </c>
       <c r="AD6">
-        <v>528.3</v>
+        <v>637.2</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>528.3</v>
+        <v>637.2</v>
       </c>
       <c r="AG6">
-        <v>-416.1</v>
+        <v>59.30000000000007</v>
       </c>
       <c r="AH6">
-        <v>0.1323231058234189</v>
+        <v>0.1263358248904574</v>
       </c>
       <c r="AI6">
-        <v>0.1427105000135066</v>
+        <v>0.1694320357370772</v>
       </c>
       <c r="AJ6">
-        <v>-0.1365112693153112</v>
+        <v>0.01327869586636215</v>
       </c>
       <c r="AK6">
-        <v>-0.1508975521305531</v>
+        <v>0.0186308083822929</v>
       </c>
       <c r="AL6">
-        <v>39.5</v>
+        <v>40.7</v>
       </c>
       <c r="AM6">
-        <v>39.5</v>
+        <v>40.7</v>
       </c>
       <c r="AN6">
-        <v>0.9682917888563048</v>
+        <v>2.80704845814978</v>
       </c>
       <c r="AO6">
-        <v>11.13924050632911</v>
+        <v>5.653562653562653</v>
       </c>
       <c r="AP6">
-        <v>-0.7626466275659824</v>
+        <v>0.2612334801762117</v>
       </c>
       <c r="AQ6">
-        <v>11.13924050632911</v>
+        <v>5.653562653562653</v>
       </c>
     </row>
     <row r="7">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Beazley plc (LSE:BEZ)</t>
+          <t>Direct Line Insurance Group plc (LSE:DLG)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1264,124 +1264,118 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.122</v>
-      </c>
-      <c r="E7">
-        <v>-0.0643</v>
-      </c>
-      <c r="F7">
-        <v>0.65</v>
+        <v>-0.00466</v>
       </c>
       <c r="G7">
-        <v>0.1085712625983909</v>
+        <v>0.05029790771788832</v>
       </c>
       <c r="H7">
-        <v>0.1085712625983909</v>
+        <v>0.05029790771788832</v>
       </c>
       <c r="I7">
-        <v>0.07084144180777832</v>
+        <v>0.001290933444182717</v>
       </c>
       <c r="J7">
-        <v>0.05785489739074135</v>
+        <v>0.001290933444182717</v>
       </c>
       <c r="K7">
-        <v>183.1</v>
+        <v>-122.1</v>
       </c>
       <c r="L7">
-        <v>0.05318191059862325</v>
+        <v>-0.02819731190245254</v>
       </c>
       <c r="M7">
-        <v>120.8</v>
+        <v>142.3</v>
       </c>
       <c r="N7">
-        <v>0.02217734532770332</v>
+        <v>0.04728203083466242</v>
       </c>
       <c r="O7">
-        <v>0.6597487711632988</v>
+        <v>-1.165438165438166</v>
       </c>
       <c r="P7">
-        <v>103</v>
+        <v>125.8</v>
       </c>
       <c r="Q7">
-        <v>0.01890949146319075</v>
+        <v>0.04179957469431154</v>
       </c>
       <c r="R7">
-        <v>0.5625341343528127</v>
+        <v>-1.03030303030303</v>
       </c>
       <c r="S7">
-        <v>17.8</v>
+        <v>16.50000000000001</v>
       </c>
       <c r="T7">
-        <v>0.1473509933774834</v>
+        <v>0.1159522136331694</v>
       </c>
       <c r="U7">
-        <v>569.4</v>
+        <v>2034.4</v>
       </c>
       <c r="V7">
-        <v>0.1045346062052506</v>
+        <v>0.6759702286018076</v>
       </c>
       <c r="W7">
-        <v>0.09352811973233896</v>
+        <v>-0.03847365767582556</v>
       </c>
       <c r="X7">
-        <v>0.09118679224338155</v>
+        <v>0.0801586944183641</v>
       </c>
       <c r="Y7">
-        <v>0.002341327488957406</v>
+        <v>-0.1186323520941897</v>
       </c>
       <c r="Z7">
-        <v>1.583670653173873</v>
+        <v>1.734716769489625</v>
       </c>
       <c r="AA7">
-        <v>0.09162310314010276</v>
+        <v>0.002239403893918757</v>
       </c>
       <c r="AB7">
-        <v>0.0859001045745989</v>
+        <v>0.07419220929811585</v>
       </c>
       <c r="AC7">
-        <v>0.005722998565503859</v>
+        <v>-0.07195280540419709</v>
       </c>
       <c r="AD7">
-        <v>641</v>
+        <v>576.4</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>641</v>
+        <v>576.4</v>
       </c>
       <c r="AG7">
-        <v>71.60000000000002</v>
+        <v>-1458</v>
       </c>
       <c r="AH7">
-        <v>0.1052890932982917</v>
+        <v>0.1607361963190184</v>
       </c>
       <c r="AI7">
-        <v>0.2414221686565478</v>
+        <v>0.1754535492511871</v>
       </c>
       <c r="AJ7">
-        <v>0.0129743050773747</v>
+        <v>-0.9396751740139212</v>
       </c>
       <c r="AK7">
-        <v>0.03432900225344011</v>
+        <v>-1.165653981451871</v>
       </c>
       <c r="AL7">
-        <v>37.2</v>
+        <v>14.9</v>
       </c>
       <c r="AM7">
-        <v>37.2</v>
+        <v>14.9</v>
       </c>
       <c r="AN7">
-        <v>2.527602523659306</v>
+        <v>3.958791208791209</v>
       </c>
       <c r="AO7">
-        <v>6.556451612903225</v>
+        <v>0.3751677852348993</v>
       </c>
       <c r="AP7">
-        <v>0.2823343848580442</v>
+        <v>-10.01373626373626</v>
       </c>
       <c r="AQ7">
-        <v>6.556451612903225</v>
+        <v>0.3751677852348993</v>
       </c>
     </row>
   </sheetData>
